--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>46</t>
+    <t>40</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.500</t>
-  </si>
-  <si>
-    <t>(0.075)</t>
-  </si>
-  <si>
-    <t>0.304</t>
-  </si>
-  <si>
-    <t>(0.069)</t>
-  </si>
-  <si>
-    <t>1.000</t>
-  </si>
-  <si>
-    <t>(0.199)</t>
-  </si>
-  <si>
-    <t>0.652</t>
-  </si>
-  <si>
-    <t>(0.187)</t>
+    <t>0.575</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>0.350</t>
+  </si>
+  <si>
+    <t>(0.076)</t>
+  </si>
+  <si>
+    <t>1.150</t>
+  </si>
+  <si>
+    <t>(0.219)</t>
+  </si>
+  <si>
+    <t>0.750</t>
+  </si>
+  <si>
+    <t>(0.211)</t>
   </si>
   <si>
     <t>70</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.357***</t>
-  </si>
-  <si>
-    <t>0.367***</t>
-  </si>
-  <si>
-    <t>3.357***</t>
-  </si>
-  <si>
-    <t>1.134***</t>
+    <t>0.282***</t>
+  </si>
+  <si>
+    <t>0.321***</t>
+  </si>
+  <si>
+    <t>3.207***</t>
+  </si>
+  <si>
+    <t>1.036**</t>
   </si>
 </sst>
 </file>
